--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92562351534</v>
+        <v>46157.93071478394</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93071478394</v>
+        <v>46157.93154701601</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93154701601</v>
+        <v>46157.93394060637</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93394060637</v>
+        <v>46157.93709214448</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93709214448</v>
+        <v>46158.28210990477</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28210990477</v>
+        <v>46158.29666196933</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29666196933</v>
+        <v>46158.29805923368</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29805923368</v>
+        <v>46158.33381752612</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33381752612</v>
+        <v>46158.36848513468</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Лукаш/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Ноябрь/Лукаш/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36848513468</v>
+        <v>46158.37281943582</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
